--- a/projects/auto_page/autopageMKII/tables/Accel_mode14-10-2026.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode14-10-2026.xlsx
@@ -2180,7 +2180,7 @@
         </is>
       </c>
     </row>
-    <row r="2" s="5">
+    <row r="2" hidden="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:42:18</t>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
     </row>
-    <row r="3" s="5">
+    <row r="3" hidden="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:42:45</t>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
     </row>
-    <row r="4" s="5">
+    <row r="4" hidden="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:43:39</t>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
     </row>
-    <row r="5" s="5">
+    <row r="5" hidden="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:44:04</t>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
     </row>
-    <row r="6" s="5">
+    <row r="6" hidden="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:44:04</t>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
     </row>
-    <row r="7" s="5">
+    <row r="7" hidden="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:44:27</t>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
     </row>
-    <row r="8" s="5">
+    <row r="8" hidden="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:44:50</t>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
     </row>
-    <row r="9" s="5">
+    <row r="9" hidden="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:45:57</t>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
     </row>
-    <row r="10" s="5">
+    <row r="10" hidden="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:46:34</t>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
     </row>
-    <row r="11" s="5">
+    <row r="11" hidden="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:47:31</t>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
     </row>
-    <row r="12" s="5">
+    <row r="12" hidden="1" s="5">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:48:14</t>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
     </row>
-    <row r="13" s="5">
+    <row r="13" hidden="1" s="5">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:48:42</t>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
     </row>
-    <row r="14" s="5">
+    <row r="14" hidden="1" s="5">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:49:20</t>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
     </row>
-    <row r="15" s="5">
+    <row r="15" hidden="1" s="5">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:50:10</t>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
     </row>
-    <row r="16" s="5">
+    <row r="16" hidden="1" s="5">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:50:48</t>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
     </row>
-    <row r="17" s="5">
+    <row r="17" hidden="1" s="5">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:51:22</t>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
     </row>
-    <row r="18" s="5">
+    <row r="18" hidden="1" s="5">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:52:11</t>
@@ -2848,7 +2848,7 @@
         </is>
       </c>
     </row>
-    <row r="19" s="5">
+    <row r="19" hidden="1" s="5">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:52:36</t>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
     </row>
-    <row r="20" s="5">
+    <row r="20" hidden="1" s="5">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:53:14</t>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
     </row>
-    <row r="21" s="5">
+    <row r="21" hidden="1" s="5">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:53:41</t>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
     </row>
-    <row r="22" s="5">
+    <row r="22" hidden="1" s="5">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:54:32</t>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
     </row>
-    <row r="23" s="5">
+    <row r="23" hidden="1" s="5">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:55:09</t>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
     </row>
-    <row r="24" s="5">
+    <row r="24" hidden="1" s="5">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:55:43</t>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
     </row>
-    <row r="25" s="5">
+    <row r="25" hidden="1" s="5">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:56:21</t>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
     </row>
-    <row r="26" s="5">
+    <row r="26" hidden="1" s="5">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:57:02</t>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
     </row>
-    <row r="27" s="5">
+    <row r="27" hidden="1" s="5">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:57:40</t>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
     </row>
-    <row r="28" s="5">
+    <row r="28" hidden="1" s="5">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:57:40</t>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
     </row>
-    <row r="29" s="5">
+    <row r="29" hidden="1" s="5">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:58:36</t>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
     </row>
-    <row r="30" s="5">
+    <row r="30" hidden="1" s="5">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:59:04</t>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
     </row>
-    <row r="31" s="5">
+    <row r="31" hidden="1" s="5">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:59:06</t>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
     </row>
-    <row r="32" s="5">
+    <row r="32" hidden="1" s="5">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 10:59:47</t>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
     </row>
-    <row r="33" s="5">
+    <row r="33" hidden="1" s="5">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:00:25</t>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
     </row>
-    <row r="34" s="5">
+    <row r="34" hidden="1" s="5">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:00:51</t>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
     </row>
-    <row r="35" s="5">
+    <row r="35" hidden="1" s="5">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:01:23</t>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
     </row>
-    <row r="36" s="5">
+    <row r="36" hidden="1" s="5">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:02:02</t>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
     </row>
-    <row r="37" s="5">
+    <row r="37" hidden="1" s="5">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:02:37</t>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
     </row>
-    <row r="38" s="5">
+    <row r="38" hidden="1" s="5">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:03:23</t>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
     </row>
-    <row r="39" s="5">
+    <row r="39" hidden="1" s="5">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:03:23</t>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
     </row>
-    <row r="40" s="5">
+    <row r="40" hidden="1" s="5">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:04:05</t>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
     </row>
-    <row r="41" s="5">
+    <row r="41" hidden="1" s="5">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:04:32</t>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
     </row>
-    <row r="42" s="5">
+    <row r="42" hidden="1" s="5">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:05:04</t>
@@ -3787,7 +3787,7 @@
         </is>
       </c>
     </row>
-    <row r="43" s="5">
+    <row r="43" hidden="1" s="5">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:05:38</t>
@@ -3826,7 +3826,7 @@
         </is>
       </c>
     </row>
-    <row r="44" s="5">
+    <row r="44" hidden="1" s="5">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:06:33</t>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
     </row>
-    <row r="45" s="5">
+    <row r="45" hidden="1" s="5">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:07:35</t>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
     </row>
-    <row r="46" s="5">
+    <row r="46" hidden="1" s="5">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:08:36</t>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
     </row>
-    <row r="47" s="5">
+    <row r="47" hidden="1" s="5">
       <c r="A47" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:09:11</t>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
     </row>
-    <row r="48" s="5">
+    <row r="48" hidden="1" s="5">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:10:01</t>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
     </row>
-    <row r="49" s="5">
+    <row r="49" hidden="1" s="5">
       <c r="A49" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:10:44</t>
@@ -4060,7 +4060,7 @@
         </is>
       </c>
     </row>
-    <row r="50" s="5">
+    <row r="50" hidden="1" s="5">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:13:39</t>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
     </row>
-    <row r="51" s="5">
+    <row r="51" hidden="1" s="5">
       <c r="A51" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:14:28</t>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
     </row>
-    <row r="52" s="5">
+    <row r="52" hidden="1" s="5">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:15:32</t>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
     </row>
-    <row r="53" s="5">
+    <row r="53" hidden="1" s="5">
       <c r="A53" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:16:21</t>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
     </row>
-    <row r="54" s="5">
+    <row r="54" hidden="1" s="5">
       <c r="A54" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:16:57</t>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
     </row>
-    <row r="55" s="5">
+    <row r="55" hidden="1" s="5">
       <c r="A55" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:17:32</t>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
     </row>
-    <row r="56" s="5">
+    <row r="56" hidden="1" s="5">
       <c r="A56" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:18:27</t>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
     </row>
-    <row r="57" s="5">
+    <row r="57" hidden="1" s="5">
       <c r="A57" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:19:15</t>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
     </row>
-    <row r="58" s="5">
+    <row r="58" hidden="1" s="5">
       <c r="A58" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:20:10</t>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
     </row>
-    <row r="59" s="5">
+    <row r="59" hidden="1" s="5">
       <c r="A59" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:21:05</t>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
     </row>
-    <row r="60" s="5">
+    <row r="60" hidden="1" s="5">
       <c r="A60" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:21:37</t>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
     </row>
-    <row r="61" s="5">
+    <row r="61" hidden="1" s="5">
       <c r="A61" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:22:28</t>
@@ -4536,7 +4536,7 @@
         </is>
       </c>
     </row>
-    <row r="62" s="5">
+    <row r="62" hidden="1" s="5">
       <c r="A62" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:23:20</t>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
     </row>
-    <row r="63" s="5">
+    <row r="63" hidden="1" s="5">
       <c r="A63" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:24:16</t>
@@ -4614,7 +4614,7 @@
         </is>
       </c>
     </row>
-    <row r="64" s="5">
+    <row r="64" hidden="1" s="5">
       <c r="A64" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:25:15</t>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
     </row>
-    <row r="65" s="5">
+    <row r="65" hidden="1" s="5">
       <c r="A65" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:26:05</t>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
     </row>
-    <row r="66" s="5">
+    <row r="66" hidden="1" s="5">
       <c r="A66" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:26:48</t>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
     </row>
-    <row r="67" s="5">
+    <row r="67" hidden="1" s="5">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:26:48</t>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
     </row>
-    <row r="68" s="5">
+    <row r="68" hidden="1" s="5">
       <c r="A68" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:27:46</t>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
     </row>
-    <row r="69" s="5">
+    <row r="69" hidden="1" s="5">
       <c r="A69" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:28:35</t>
@@ -4840,7 +4840,7 @@
         </is>
       </c>
     </row>
-    <row r="70" s="5">
+    <row r="70" hidden="1" s="5">
       <c r="A70" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:29:36</t>
@@ -4875,7 +4875,7 @@
         </is>
       </c>
     </row>
-    <row r="71" s="5">
+    <row r="71" hidden="1" s="5">
       <c r="A71" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:30:29</t>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
     </row>
-    <row r="72" s="5">
+    <row r="72" hidden="1" s="5">
       <c r="A72" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:31:22</t>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
     </row>
-    <row r="73" s="5">
+    <row r="73" hidden="1" s="5">
       <c r="A73" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:31:58</t>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
     </row>
-    <row r="74" s="5">
+    <row r="74" hidden="1" s="5">
       <c r="A74" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:32:37</t>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
     </row>
-    <row r="75" s="5">
+    <row r="75" hidden="1" s="5">
       <c r="A75" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:33:12</t>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
     </row>
-    <row r="76" s="5">
+    <row r="76" hidden="1" s="5">
       <c r="A76" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:34:02</t>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
     </row>
-    <row r="77" s="5">
+    <row r="77" hidden="1" s="5">
       <c r="A77" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:34:54</t>
@@ -5120,7 +5120,7 @@
         </is>
       </c>
     </row>
-    <row r="78" s="5">
+    <row r="78" hidden="1" s="5">
       <c r="A78" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:35:31</t>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
     </row>
-    <row r="79" s="5">
+    <row r="79" hidden="1" s="5">
       <c r="A79" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:36:36</t>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
     </row>
-    <row r="80" s="5">
+    <row r="80" hidden="1" s="5">
       <c r="A80" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:37:29</t>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
     </row>
-    <row r="81" s="5">
+    <row r="81" hidden="1" s="5">
       <c r="A81" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:37:53</t>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
     </row>
-    <row r="82" s="5">
+    <row r="82" hidden="1" s="5">
       <c r="A82" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:38:21</t>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
     </row>
-    <row r="83" s="5">
+    <row r="83" hidden="1" s="5">
       <c r="A83" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:39:10</t>
@@ -5352,7 +5352,7 @@
         </is>
       </c>
     </row>
-    <row r="84" s="5">
+    <row r="84" hidden="1" s="5">
       <c r="A84" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:40:13</t>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
     </row>
-    <row r="85" s="5">
+    <row r="85" hidden="1" s="5">
       <c r="A85" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:40:56</t>
@@ -5427,7 +5427,7 @@
         </is>
       </c>
     </row>
-    <row r="86" s="5">
+    <row r="86" hidden="1" s="5">
       <c r="A86" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:41:33</t>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
     </row>
-    <row r="87" s="5">
+    <row r="87" hidden="1" s="5">
       <c r="A87" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:42:07</t>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
     </row>
-    <row r="88" s="5">
+    <row r="88" hidden="1" s="5">
       <c r="A88" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:42:58</t>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
     </row>
-    <row r="89" s="5">
+    <row r="89" hidden="1" s="5">
       <c r="A89" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 11:44:21</t>
@@ -5567,7 +5567,7 @@
         </is>
       </c>
     </row>
-    <row r="90" s="5">
+    <row r="90" hidden="1" s="5">
       <c r="A90" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:04:47</t>
@@ -5606,7 +5606,7 @@
       <c r="H90" s="4" t="inlineStr"/>
       <c r="I90" s="4" t="inlineStr"/>
     </row>
-    <row r="91" s="5">
+    <row r="91" hidden="1" s="5">
       <c r="A91" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:11:23</t>
@@ -5645,7 +5645,7 @@
       <c r="H91" s="4" t="inlineStr"/>
       <c r="I91" s="4" t="inlineStr"/>
     </row>
-    <row r="92" s="5">
+    <row r="92" hidden="1" s="5">
       <c r="A92" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:14:21</t>
@@ -5684,7 +5684,7 @@
       <c r="H92" s="4" t="inlineStr"/>
       <c r="I92" s="4" t="inlineStr"/>
     </row>
-    <row r="93" s="5">
+    <row r="93" hidden="1" s="5">
       <c r="A93" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:16:09</t>
@@ -5723,7 +5723,7 @@
       <c r="H93" s="4" t="inlineStr"/>
       <c r="I93" s="4" t="inlineStr"/>
     </row>
-    <row r="94" s="5">
+    <row r="94" hidden="1" s="5">
       <c r="A94" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:16:09</t>
@@ -5758,7 +5758,7 @@
       <c r="H94" s="4" t="inlineStr"/>
       <c r="I94" s="4" t="inlineStr"/>
     </row>
-    <row r="95" s="5">
+    <row r="95" hidden="1" s="5">
       <c r="A95" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:22:30</t>
@@ -5797,7 +5797,7 @@
       <c r="H95" s="4" t="inlineStr"/>
       <c r="I95" s="4" t="inlineStr"/>
     </row>
-    <row r="96" s="5">
+    <row r="96" hidden="1" s="5">
       <c r="A96" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:23:38</t>
@@ -5836,7 +5836,7 @@
       <c r="H96" s="4" t="inlineStr"/>
       <c r="I96" s="4" t="inlineStr"/>
     </row>
-    <row r="97" s="5">
+    <row r="97" hidden="1" s="5">
       <c r="A97" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:24:40</t>
@@ -5875,7 +5875,7 @@
       <c r="H97" s="4" t="inlineStr"/>
       <c r="I97" s="4" t="inlineStr"/>
     </row>
-    <row r="98" s="5">
+    <row r="98" hidden="1" s="5">
       <c r="A98" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:26:14</t>
@@ -5914,7 +5914,7 @@
       <c r="H98" s="4" t="inlineStr"/>
       <c r="I98" s="4" t="inlineStr"/>
     </row>
-    <row r="99" s="5">
+    <row r="99" hidden="1" s="5">
       <c r="A99" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:27:19</t>
@@ -5953,7 +5953,7 @@
       <c r="H99" s="4" t="inlineStr"/>
       <c r="I99" s="4" t="inlineStr"/>
     </row>
-    <row r="100" s="5">
+    <row r="100" hidden="1" s="5">
       <c r="A100" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:30:08</t>
@@ -5992,7 +5992,7 @@
       <c r="H100" s="4" t="inlineStr"/>
       <c r="I100" s="4" t="inlineStr"/>
     </row>
-    <row r="101" s="5">
+    <row r="101" hidden="1" s="5">
       <c r="A101" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:31:26</t>
@@ -6031,7 +6031,7 @@
       <c r="H101" s="4" t="inlineStr"/>
       <c r="I101" s="4" t="inlineStr"/>
     </row>
-    <row r="102" s="5">
+    <row r="102" hidden="1" s="5">
       <c r="A102" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:32:42</t>
@@ -6070,7 +6070,7 @@
       <c r="H102" s="4" t="inlineStr"/>
       <c r="I102" s="4" t="inlineStr"/>
     </row>
-    <row r="103" s="5">
+    <row r="103" hidden="1" s="5">
       <c r="A103" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:35:20</t>
@@ -6109,7 +6109,7 @@
       <c r="H103" s="4" t="inlineStr"/>
       <c r="I103" s="4" t="inlineStr"/>
     </row>
-    <row r="104" s="5">
+    <row r="104" hidden="1" s="5">
       <c r="A104" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:35:20</t>
@@ -6144,7 +6144,7 @@
       <c r="H104" s="4" t="inlineStr"/>
       <c r="I104" s="4" t="inlineStr"/>
     </row>
-    <row r="105" s="5">
+    <row r="105" hidden="1" s="5">
       <c r="A105" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:35:20</t>
@@ -6179,7 +6179,7 @@
       <c r="H105" s="4" t="inlineStr"/>
       <c r="I105" s="4" t="inlineStr"/>
     </row>
-    <row r="106" s="5">
+    <row r="106" hidden="1" s="5">
       <c r="A106" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:35:20</t>
@@ -6214,7 +6214,7 @@
       <c r="H106" s="4" t="inlineStr"/>
       <c r="I106" s="4" t="inlineStr"/>
     </row>
-    <row r="107" s="5">
+    <row r="107" hidden="1" s="5">
       <c r="A107" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:36:52</t>
@@ -6253,7 +6253,7 @@
       <c r="H107" s="4" t="inlineStr"/>
       <c r="I107" s="4" t="inlineStr"/>
     </row>
-    <row r="108" s="5">
+    <row r="108" hidden="1" s="5">
       <c r="A108" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:36:52</t>
@@ -6288,7 +6288,7 @@
       <c r="H108" s="4" t="inlineStr"/>
       <c r="I108" s="4" t="inlineStr"/>
     </row>
-    <row r="109" s="5">
+    <row r="109" hidden="1" s="5">
       <c r="A109" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:36:52</t>
@@ -6323,7 +6323,7 @@
       <c r="H109" s="4" t="inlineStr"/>
       <c r="I109" s="4" t="inlineStr"/>
     </row>
-    <row r="110" s="5">
+    <row r="110" hidden="1" s="5">
       <c r="A110" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:37:55</t>
@@ -6362,7 +6362,7 @@
       <c r="H110" s="4" t="inlineStr"/>
       <c r="I110" s="4" t="inlineStr"/>
     </row>
-    <row r="111" s="5">
+    <row r="111" hidden="1" s="5">
       <c r="A111" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:40:27</t>
@@ -6401,7 +6401,7 @@
       <c r="H111" s="4" t="inlineStr"/>
       <c r="I111" s="4" t="inlineStr"/>
     </row>
-    <row r="112" s="5">
+    <row r="112" hidden="1" s="5">
       <c r="A112" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:41:28</t>
@@ -6440,7 +6440,7 @@
       <c r="H112" s="4" t="inlineStr"/>
       <c r="I112" s="4" t="inlineStr"/>
     </row>
-    <row r="113" s="5">
+    <row r="113" hidden="1" s="5">
       <c r="A113" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:43:22</t>
@@ -6479,7 +6479,7 @@
       <c r="H113" s="4" t="inlineStr"/>
       <c r="I113" s="4" t="inlineStr"/>
     </row>
-    <row r="114" s="5">
+    <row r="114" hidden="1" s="5">
       <c r="A114" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 16:43:22</t>
@@ -6514,7 +6514,7 @@
       <c r="H114" s="4" t="inlineStr"/>
       <c r="I114" s="4" t="inlineStr"/>
     </row>
-    <row r="115" s="5">
+    <row r="115" hidden="1" s="5">
       <c r="A115" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 17:06:11</t>
@@ -6553,7 +6553,7 @@
       <c r="H115" s="4" t="inlineStr"/>
       <c r="I115" s="4" t="inlineStr"/>
     </row>
-    <row r="116" s="5">
+    <row r="116" hidden="1" s="5">
       <c r="A116" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 17:07:13</t>
@@ -6592,7 +6592,7 @@
       <c r="H116" s="4" t="inlineStr"/>
       <c r="I116" s="4" t="inlineStr"/>
     </row>
-    <row r="117" s="5">
+    <row r="117" hidden="1" s="5">
       <c r="A117" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 17:08:24</t>
@@ -6631,7 +6631,7 @@
       <c r="H117" s="4" t="inlineStr"/>
       <c r="I117" s="4" t="inlineStr"/>
     </row>
-    <row r="118" s="5">
+    <row r="118" hidden="1" s="5">
       <c r="A118" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 17:09:32</t>
@@ -6670,7 +6670,7 @@
       <c r="H118" s="4" t="inlineStr"/>
       <c r="I118" s="4" t="inlineStr"/>
     </row>
-    <row r="119" s="5">
+    <row r="119" hidden="1" s="5">
       <c r="A119" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 17:14:04</t>
@@ -6709,7 +6709,7 @@
       <c r="H119" s="4" t="inlineStr"/>
       <c r="I119" s="4" t="inlineStr"/>
     </row>
-    <row r="120" s="5">
+    <row r="120" hidden="1" s="5">
       <c r="A120" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 17:42:19</t>
@@ -6748,7 +6748,7 @@
       <c r="H120" s="4" t="inlineStr"/>
       <c r="I120" s="4" t="inlineStr"/>
     </row>
-    <row r="121" s="5">
+    <row r="121" hidden="1" s="5">
       <c r="A121" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 17:50:23</t>
@@ -6787,7 +6787,7 @@
       <c r="H121" s="4" t="inlineStr"/>
       <c r="I121" s="4" t="inlineStr"/>
     </row>
-    <row r="122" s="5">
+    <row r="122" hidden="1" s="5">
       <c r="A122" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 17:52:09</t>
@@ -6826,7 +6826,7 @@
       <c r="H122" s="4" t="inlineStr"/>
       <c r="I122" s="4" t="inlineStr"/>
     </row>
-    <row r="123" s="5">
+    <row r="123" hidden="1" s="5">
       <c r="A123" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 17:54:51</t>
@@ -6865,7 +6865,7 @@
       <c r="H123" s="4" t="inlineStr"/>
       <c r="I123" s="4" t="inlineStr"/>
     </row>
-    <row r="124" s="5">
+    <row r="124" hidden="1" s="5">
       <c r="A124" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 17:54:51</t>
@@ -6900,7 +6900,7 @@
       <c r="H124" s="4" t="inlineStr"/>
       <c r="I124" s="4" t="inlineStr"/>
     </row>
-    <row r="125" s="5">
+    <row r="125" hidden="1" s="5">
       <c r="A125" s="4" t="inlineStr">
         <is>
           <t>2026-10-14 17:58:00</t>
